--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82FD0822-F609-C748-8ECB-43A412C9BC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605548AD-CA5F-3A48-9607-C090A3F4E02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1080,25 +1080,25 @@
         <v>172</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>173</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>174</v>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.125</v>
+        <v>0.13040123456790123</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
@@ -1140,7 +1140,10 @@
       <c r="D2" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="E2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -1155,6 +1158,24 @@
       <c r="D3" s="8" t="s">
         <v>181</v>
       </c>
+      <c r="E3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1169,7 +1190,7 @@
       <c r="D4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605548AD-CA5F-3A48-9607-C090A3F4E02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6616EAD0-2F67-2A4F-BE83-9F3AA042F9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.13040123456790123</v>
+        <v>0.13425925925925927</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
@@ -1143,7 +1143,21 @@
       <c r="E2" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6616EAD0-2F67-2A4F-BE83-9F3AA042F9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C7A485-4259-6B4A-929A-795A4874C7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.13425925925925927</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
@@ -1204,7 +1204,24 @@
       <c r="D4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="E4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C7A485-4259-6B4A-929A-795A4874C7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB1F262-7BF7-AD4C-9FD1-47A531756F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -1054,6 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1127,7 +1128,7 @@
         <v>0.1388888888888889</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1159,7 +1160,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1191,7 +1192,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2316,7 +2317,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB1F262-7BF7-AD4C-9FD1-47A531756F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6593FB-E7CC-CB48-B542-5BE803C2B996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.1388888888888889</v>
+        <v>0.14891975308641975</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1224,7 +1224,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1235,6 +1235,27 @@
         <v>180</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>180</v>
       </c>
     </row>
@@ -1249,6 +1270,24 @@
         <v>180</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6593FB-E7CC-CB48-B542-5BE803C2B996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A7E4E5-CDB6-FB45-9984-E0BF1153E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1054,7 +1054,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1121,14 +1120,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.14891975308641975</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+        <v>0.16743827160493827</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1160,7 +1159,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1192,7 +1191,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1224,7 +1223,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1304,6 +1303,24 @@
       <c r="D7" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1318,6 +1335,24 @@
       <c r="D8" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1332,6 +1367,24 @@
       <c r="D9" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -1346,6 +1399,24 @@
       <c r="D10" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -2356,11 +2427,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-    <filterColumn colId="4">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A7E4E5-CDB6-FB45-9984-E0BF1153E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123F89B9-BE5F-E54D-AF7B-AD6CA7808344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1054,6 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1120,14 +1121,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.16743827160493827</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+        <v>0.17206790123456789</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1159,7 +1160,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1191,7 +1192,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,7 +1224,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1258,7 +1259,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1290,7 +1291,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1431,6 +1432,24 @@
       <c r="D11" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -2427,7 +2446,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+    <filterColumn colId="4">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123F89B9-BE5F-E54D-AF7B-AD6CA7808344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D197165-4EDB-DF48-8690-BB2CA5F37F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.17206790123456789</v>
+        <v>0.17669753086419754</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1419,7 +1419,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1462,6 +1462,24 @@
         <v>180</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D197165-4EDB-DF48-8690-BB2CA5F37F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7652FA6D-D9B7-9140-8C47-BF8A2FA67B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.17669753086419754</v>
+        <v>0.18595679012345678</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1159,6 +1159,9 @@
       <c r="J2" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K2" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -1255,9 +1258,6 @@
       <c r="J5" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1483,7 +1483,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1494,6 +1494,24 @@
         <v>180</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>180</v>
       </c>
     </row>
@@ -1508,6 +1526,24 @@
         <v>180</v>
       </c>
       <c r="D14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7652FA6D-D9B7-9140-8C47-BF8A2FA67B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9372066B-541C-234E-90BE-A01E80F26413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.18595679012345678</v>
+        <v>0.24614197530864199</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1515,7 +1515,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -1560,8 +1560,26 @@
       <c r="D15" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="E15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1574,8 +1592,26 @@
       <c r="D16" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1588,8 +1624,26 @@
       <c r="D17" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1602,8 +1656,26 @@
       <c r="D18" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E18" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1616,8 +1688,26 @@
       <c r="D19" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E19" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -1630,8 +1720,26 @@
       <c r="D20" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -1644,8 +1752,26 @@
       <c r="D21" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -1658,8 +1784,26 @@
       <c r="D22" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -1672,8 +1816,26 @@
       <c r="D23" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -1686,8 +1848,26 @@
       <c r="D24" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -1700,8 +1880,26 @@
       <c r="D25" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1714,8 +1912,26 @@
       <c r="D26" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -1728,8 +1944,26 @@
       <c r="D27" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1743,7 +1977,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -1757,7 +1991,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -1771,7 +2005,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -1785,7 +2019,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9372066B-541C-234E-90BE-A01E80F26413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E455C1-499A-BC4D-8D7C-BB20F6A0C6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.24614197530864199</v>
+        <v>0.25077160493827161</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1974,6 +1974,24 @@
         <v>180</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E455C1-499A-BC4D-8D7C-BB20F6A0C6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166DEC2B-6849-B748-A159-D4E168282F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166DEC2B-6849-B748-A159-D4E168282F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15348619-B49A-A846-BB32-7BFE41695B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -1931,7 +1931,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15348619-B49A-A846-BB32-7BFE41695B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C8B178-E33F-3B47-92CD-D33604AE7161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.25077160493827161</v>
+        <v>0.2785493827160494</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2008,6 +2008,24 @@
       <c r="D29" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -2022,6 +2040,24 @@
       <c r="D30" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
@@ -2036,6 +2072,24 @@
       <c r="D31" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E31" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -2050,8 +2104,26 @@
       <c r="D32" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -2064,8 +2136,26 @@
       <c r="D33" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -2078,8 +2168,26 @@
       <c r="D34" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -2093,7 +2201,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -2107,7 +2215,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -2121,7 +2229,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2135,7 +2243,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -2149,7 +2257,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -2163,7 +2271,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -2177,7 +2285,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -2191,7 +2299,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -2205,7 +2313,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -2219,7 +2327,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -2233,7 +2341,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -2247,7 +2355,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="26" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -2261,7 +2369,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C8B178-E33F-3B47-92CD-D33604AE7161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE3C68F-9FD5-C948-81C3-6791BFBBA759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.2785493827160494</v>
+        <v>0.29475308641975306</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -1995,7 +1995,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -2200,8 +2200,29 @@
       <c r="D35" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -2214,8 +2235,29 @@
       <c r="D36" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -2228,8 +2270,29 @@
       <c r="D37" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2243,7 +2306,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -2257,7 +2320,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -2271,7 +2334,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -2285,7 +2348,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -2299,7 +2362,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -2313,7 +2376,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -2327,7 +2390,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -2341,7 +2404,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -2355,7 +2418,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="26" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -2369,7 +2432,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE3C68F-9FD5-C948-81C3-6791BFBBA759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF5C06B-E78A-AD4B-B694-84103FF05629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.29475308641975306</v>
+        <v>0.30401234567901236</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2187,7 +2187,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2305,8 +2305,26 @@
       <c r="D38" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="E38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -2317,6 +2335,24 @@
         <v>180</v>
       </c>
       <c r="D39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J39" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF5C06B-E78A-AD4B-B694-84103FF05629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A04FB99-B64D-CD46-9220-853CC58C45A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.30401234567901236</v>
+        <v>0.30864197530864196</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2367,6 +2367,24 @@
         <v>180</v>
       </c>
       <c r="D40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J40" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A04FB99-B64D-CD46-9220-853CC58C45A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F28C85-DC0A-CB49-9A90-DB6160E23D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.30864197530864196</v>
+        <v>0.3317901234567901</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2356,7 +2356,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -2401,6 +2401,24 @@
       <c r="D41" s="8" t="s">
         <v>181</v>
       </c>
+      <c r="E41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="42" spans="1:11" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
@@ -2415,6 +2433,24 @@
       <c r="D42" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -2429,6 +2465,24 @@
       <c r="D43" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2443,6 +2497,24 @@
       <c r="D44" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -2455,6 +2527,24 @@
         <v>180</v>
       </c>
       <c r="D45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J45" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F28C85-DC0A-CB49-9A90-DB6160E23D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D1CA1D-6767-6F4E-803F-98480E9102F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -2388,7 +2388,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D1CA1D-6767-6F4E-803F-98480E9102F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86AF62C-27A5-3B45-B8B3-92554AD0A549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.3317901234567901</v>
+        <v>0.35956790123456789</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2548,7 +2548,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -2561,8 +2561,26 @@
       <c r="D46" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="26" x14ac:dyDescent="0.2">
+      <c r="E46" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -2575,8 +2593,26 @@
       <c r="D47" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="E47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
@@ -2589,8 +2625,26 @@
       <c r="D48" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -2603,8 +2657,26 @@
       <c r="D49" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -2617,8 +2689,26 @@
       <c r="D50" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -2631,8 +2721,26 @@
       <c r="D51" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -2646,7 +2754,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -2660,7 +2768,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -2674,7 +2782,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="26" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -2688,7 +2796,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2702,7 +2810,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -2716,7 +2824,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -2730,7 +2838,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -2744,7 +2852,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -2758,7 +2866,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -2772,7 +2880,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -2786,7 +2894,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -2800,7 +2908,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B86AF62C-27A5-3B45-B8B3-92554AD0A549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79236F43-4400-FA4E-BF16-CA562391AA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -2676,7 +2676,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79236F43-4400-FA4E-BF16-CA562391AA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A366C5C-54E0-2C45-BE56-8C9B46CEAFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.35956790123456789</v>
+        <v>0.36882716049382713</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2740,7 +2740,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -2753,8 +2753,26 @@
       <c r="D52" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -2765,6 +2783,24 @@
         <v>180</v>
       </c>
       <c r="D53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J53" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A366C5C-54E0-2C45-BE56-8C9B46CEAFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E268584C-4F12-B248-BA20-A9BFB048D6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.36882716049382713</v>
+        <v>0.37808641975308643</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2817,6 +2817,24 @@
       <c r="D54" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="55" spans="1:10" ht="26" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
@@ -2829,6 +2847,24 @@
         <v>180</v>
       </c>
       <c r="D55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J55" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E268584C-4F12-B248-BA20-A9BFB048D6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A084DFF0-F7EF-EC40-A671-C850AD8785AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.37808641975308643</v>
+        <v>0.39660493827160492</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2804,7 +2804,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2881,8 +2881,26 @@
       <c r="D56" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -2895,8 +2913,26 @@
       <c r="D57" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E57" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -2909,8 +2945,26 @@
       <c r="D58" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="E58" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -2921,6 +2975,24 @@
         <v>180</v>
       </c>
       <c r="D59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J59" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A084DFF0-F7EF-EC40-A671-C850AD8785AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14CFC7C-4365-A24A-BFFA-15A421FF275B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.39660493827160492</v>
+        <v>0.40586419753086422</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -3009,6 +3009,24 @@
       <c r="D60" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E60" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="61" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
@@ -3021,6 +3039,24 @@
         <v>180</v>
       </c>
       <c r="D61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J61" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14CFC7C-4365-A24A-BFFA-15A421FF275B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEF08F7-FAB2-374D-828B-1C794D0F1295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.40586419753086422</v>
+        <v>0.41049382716049382</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -3071,6 +3071,24 @@
         <v>180</v>
       </c>
       <c r="D62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J62" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEF08F7-FAB2-374D-828B-1C794D0F1295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A28C1-D366-9541-923F-A5E8150A217A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.41049382716049382</v>
+        <v>0.41975308641975306</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -3105,6 +3105,24 @@
       <c r="D63" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="64" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
@@ -3117,6 +3135,24 @@
         <v>180</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J64" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A28C1-D366-9541-923F-A5E8150A217A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4EAA73-2653-4A42-8352-1F3EE39C9638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.41975308641975306</v>
+        <v>0.42438271604938271</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -2996,7 +2996,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>128</v>
       </c>
@@ -3169,8 +3169,26 @@
       <c r="D65" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -3184,7 +3202,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>132</v>
       </c>
@@ -3198,7 +3216,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
@@ -3212,7 +3230,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>136</v>
       </c>
@@ -3226,7 +3244,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
@@ -3240,7 +3258,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>140</v>
       </c>
@@ -3254,7 +3272,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -3268,7 +3286,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>144</v>
       </c>
@@ -3282,7 +3300,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
@@ -3296,7 +3314,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>148</v>
       </c>
@@ -3310,7 +3328,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -3324,7 +3342,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>152</v>
       </c>
@@ -3338,7 +3356,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
@@ -3352,7 +3370,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>156</v>
       </c>
@@ -3366,7 +3384,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4EAA73-2653-4A42-8352-1F3EE39C9638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F209D0BC-8CA2-444E-A4D8-DFEC31A2D54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -3156,7 +3156,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>128</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F209D0BC-8CA2-444E-A4D8-DFEC31A2D54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A9AD50-8601-2C4A-9451-1F0B38D41096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1121,11 +1121,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>550</v>
+        <v>628</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.42438271604938271</v>
+        <v>0.48456790123456789</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -3201,6 +3201,24 @@
       <c r="D66" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E66" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="67" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
@@ -3215,6 +3233,24 @@
       <c r="D67" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="68" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
@@ -3229,6 +3265,24 @@
       <c r="D68" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E68" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="69" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -3243,6 +3297,24 @@
       <c r="D69" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E69" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="70" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
@@ -3257,6 +3329,24 @@
       <c r="D70" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="71" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
@@ -3271,6 +3361,24 @@
       <c r="D71" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="72" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -3285,6 +3393,24 @@
       <c r="D72" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E72" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="73" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
@@ -3299,6 +3425,24 @@
       <c r="D73" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E73" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="74" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
@@ -3313,6 +3457,24 @@
       <c r="D74" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="75" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
@@ -3327,6 +3489,24 @@
       <c r="D75" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E75" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="76" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
@@ -3341,6 +3521,24 @@
       <c r="D76" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
@@ -3355,6 +3553,24 @@
       <c r="D77" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="78" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
@@ -3367,6 +3583,24 @@
         <v>180</v>
       </c>
       <c r="D78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J78" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A9AD50-8601-2C4A-9451-1F0B38D41096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E296921C-EF7A-B740-932A-CF86F1362787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="182">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1054,7 +1054,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1121,14 +1120,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.48456790123456789</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+        <v>0.50308641975308643</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1163,7 +1162,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1194,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1227,7 +1226,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1259,7 +1258,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1291,7 +1290,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -1323,7 +1322,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1355,7 +1354,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1387,7 +1386,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1419,7 +1418,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1451,7 +1450,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1483,7 +1482,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -1515,7 +1514,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1547,7 +1546,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1611,7 +1610,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1643,7 +1642,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1707,7 +1706,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -1739,7 +1738,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -1803,7 +1802,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -1963,7 +1962,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1995,7 +1994,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -2091,7 +2090,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -2187,7 +2186,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -2257,7 +2256,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -2292,7 +2291,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -2356,7 +2355,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -2484,7 +2483,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -2516,7 +2515,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -2580,7 +2579,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="26" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -2612,7 +2611,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -2708,7 +2707,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -2772,7 +2771,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -2804,7 +2803,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -2836,7 +2835,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="26" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2900,7 +2899,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -2996,7 +2995,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -3028,7 +3027,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -3124,7 +3123,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
@@ -3156,7 +3155,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>128</v>
       </c>
@@ -3617,6 +3616,24 @@
       <c r="D79" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E79" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="80" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
@@ -3631,8 +3648,26 @@
       <c r="D80" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>160</v>
       </c>
@@ -3645,8 +3680,26 @@
       <c r="D81" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="14" x14ac:dyDescent="0.2">
+      <c r="E81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
@@ -3659,13 +3712,27 @@
       <c r="D82" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="E82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-    <filterColumn colId="4">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E296921C-EF7A-B740-932A-CF86F1362787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6EDE9F-DE7C-FB4D-9966-E2CE00FE0656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$R$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sayfa2!$B$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -588,13 +590,672 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>İsim</t>
+  </si>
+  <si>
+    <t>Konum</t>
+  </si>
+  <si>
+    <t>Pazarkule</t>
+  </si>
+  <si>
+    <r>
+      <t>Karaağaç</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Merkez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Edirne</t>
+    </r>
+  </si>
+  <si>
+    <t>İpsala</t>
+  </si>
+  <si>
+    <r>
+      <t>İpsala</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Edirne</t>
+    </r>
+  </si>
+  <si>
+    <t>Kapıkule</t>
+  </si>
+  <si>
+    <r>
+      <t>Kemalköy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Merkez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Edirne</t>
+    </r>
+  </si>
+  <si>
+    <t>Hamzabeyli</t>
+  </si>
+  <si>
+    <r>
+      <t>Hamzabeyli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lalapaşa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Edirne</t>
+    </r>
+  </si>
+  <si>
+    <t>Dereköy</t>
+  </si>
+  <si>
+    <r>
+      <t>Dereköy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Merkez</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kırklareli</t>
+    </r>
+  </si>
+  <si>
+    <t>Türkgözü</t>
+  </si>
+  <si>
+    <t>Türkgözü,</t>
+  </si>
+  <si>
+    <r>
+      <t>Posof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ardahan</t>
+    </r>
+  </si>
+  <si>
+    <t>Aktaş</t>
+  </si>
+  <si>
+    <t>Aktaş,</t>
+  </si>
+  <si>
+    <r>
+      <t>Çıldır</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ardahan</t>
+    </r>
+  </si>
+  <si>
+    <t>Sarp</t>
+  </si>
+  <si>
+    <r>
+      <t>Sarp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kemalpaşa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Artvin</t>
+    </r>
+  </si>
+  <si>
+    <t>Dilucu</t>
+  </si>
+  <si>
+    <r>
+      <t>Gödekli</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Aralık</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Iğdır</t>
+    </r>
+  </si>
+  <si>
+    <t>Gürbulak</t>
+  </si>
+  <si>
+    <r>
+      <t>Gürbulak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Doğubayazıt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ağrı</t>
+    </r>
+  </si>
+  <si>
+    <t>Kapıköy</t>
+  </si>
+  <si>
+    <r>
+      <t>Kapıköy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Saray</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Van</t>
+    </r>
+  </si>
+  <si>
+    <t>Esendere</t>
+  </si>
+  <si>
+    <r>
+      <t>Yüksekova</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hakkâri</t>
+    </r>
+  </si>
+  <si>
+    <t>Karkamış</t>
+  </si>
+  <si>
+    <t>Gaziantep</t>
+  </si>
+  <si>
+    <t>Şemdinli-Derecik</t>
+  </si>
+  <si>
+    <t>Hakkâri</t>
+  </si>
+  <si>
+    <t>Çukurca-Üzümlü</t>
+  </si>
+  <si>
+    <t>Yayladağı</t>
+  </si>
+  <si>
+    <r>
+      <t>Yayladağı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hatay</t>
+    </r>
+  </si>
+  <si>
+    <t>Cilvegözü</t>
+  </si>
+  <si>
+    <r>
+      <t>Reyhanlı</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Hatay</t>
+    </r>
+  </si>
+  <si>
+    <t>Öncüpınar</t>
+  </si>
+  <si>
+    <t>Kilis</t>
+  </si>
+  <si>
+    <t>Çobanbey</t>
+  </si>
+  <si>
+    <t>Nusaybin</t>
+  </si>
+  <si>
+    <t>Mardin</t>
+  </si>
+  <si>
+    <t>Şenyurt</t>
+  </si>
+  <si>
+    <t>Akçakale</t>
+  </si>
+  <si>
+    <t>Şanlıurfa</t>
+  </si>
+  <si>
+    <t>Ceylanpınar</t>
+  </si>
+  <si>
+    <t>Mürşitpınar</t>
+  </si>
+  <si>
+    <t>Habur</t>
+  </si>
+  <si>
+    <r>
+      <t>Silopi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Şırnak</t>
+    </r>
+  </si>
+  <si>
+    <t>Gülyazı</t>
+  </si>
+  <si>
+    <t>Akyaka</t>
+  </si>
+  <si>
+    <t>Kars</t>
+  </si>
+  <si>
+    <t>Alican</t>
+  </si>
+  <si>
+    <r>
+      <t>Karakoyunlu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF202122"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF3366CC"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Iğdır</t>
+    </r>
+  </si>
+  <si>
+    <t>Borualan</t>
+  </si>
+  <si>
+    <t>Iğdır</t>
+  </si>
+  <si>
+    <t>Zeytindalı</t>
+  </si>
+  <si>
+    <t>Hatay</t>
+  </si>
+  <si>
+    <t>Demiryolu</t>
+  </si>
+  <si>
+    <t>Edirne</t>
+  </si>
+  <si>
+    <t>Çıldır-Aktaş</t>
+  </si>
+  <si>
+    <t>Ardahan</t>
+  </si>
+  <si>
+    <t>Van</t>
+  </si>
+  <si>
+    <t>Uzunköprü</t>
+  </si>
+  <si>
+    <t>İslahiye</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -645,6 +1306,47 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF3366CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF101418"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF101418"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -684,12 +1386,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -718,8 +1421,16 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Köprü" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_mesafe cetveli-2004" xfId="2" xr:uid="{5268B61A-F969-B246-9532-DAC26E1E8E9F}"/>
     <cellStyle name="Yüzde" xfId="1" builtinId="5"/>
@@ -735,6 +1446,1724 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Resim 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EF34098-A32D-E040-A648-FDD7BE98F1DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="457200"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Resim 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D64F4855-6953-B63A-DF60-FCCB62625BC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="457200"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Resim 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{205F5906-2725-FC98-A90B-1A072BD520EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="711200"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Resim 4">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8C512F9-7C0C-343F-A9C8-1E0C66F4AE6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6172200" y="711200"/>
+          <a:ext cx="406400" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2053" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48DFB8EE-839A-DE49-6AD6-701F18A4B84E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="965200"/>
+          <a:ext cx="292100" cy="177800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2054" name="AutoShape 6">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DFB6CDF-932B-67CB-EE78-9E9F5A2D814B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="965200"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2055" name="AutoShape 7">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84F1F5BC-10CB-D1DB-C3DB-D91236C6C077}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="1473200"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2056" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6EF50F7-EC3F-084C-A2FA-77129C894A51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="1727200"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2057" name="AutoShape 9">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48E9F95F-A5C7-0345-9CF5-18082C5A4778}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="1727200"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2058" name="AutoShape 10">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1BC8D05-B553-69D9-CC33-A15E733390B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6997700" y="1727200"/>
+          <a:ext cx="381000" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2059" name="AutoShape 11">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E8E4B91-9320-2E68-32EC-B10B3313DD86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="2184400"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2060" name="AutoShape 12">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F492142-09FC-C522-6A2B-179CC4FC8535}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6172200" y="2184400"/>
+          <a:ext cx="381000" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>241300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2061" name="AutoShape 13">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03035BA5-2BA6-324B-A0D2-6E441F471715}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="2641600"/>
+          <a:ext cx="381000" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2062" name="AutoShape 14">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604B92A8-9D4A-E2E6-878C-93BB7EC66801}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6172200" y="2641600"/>
+          <a:ext cx="406400" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2063" name="AutoShape 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4FD1570-4FDC-F2A6-178E-7A3A21D15399}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="2921000"/>
+          <a:ext cx="292100" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2064" name="AutoShape 16">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{050B97CA-E98D-D50C-6A64-0169E7D6B560}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="2921000"/>
+          <a:ext cx="406400" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2065" name="AutoShape 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCA229F9-9ADA-8B61-D699-EB36B604BE43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="3149600"/>
+          <a:ext cx="292100" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2066" name="AutoShape 18">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C78DBE3-E0AE-9295-049F-A885AA4D8F89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="3149600"/>
+          <a:ext cx="228600" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2067" name="AutoShape 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE7DE7FD-42F7-FB77-0D75-0CF9C5805013}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="3530600"/>
+          <a:ext cx="228600" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2068" name="AutoShape 20">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA78846D-A3FE-5006-B91B-E056BB858C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5778500" y="3911600"/>
+          <a:ext cx="228600" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2069" name="AutoShape 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FCFD1C5-0FC3-6519-5CF6-46671E59D9E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="4292600"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2070" name="AutoShape 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C01257E-4C3D-F80A-DFFB-E6CB5BDEE992}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="4165600"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2071" name="AutoShape 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{494C6FA6-33B9-0AE8-B8FB-5496E209557E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="4673600"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2072" name="AutoShape 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEE2C18F-38B2-847A-2DAC-764695E14CC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="6959600"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2073" name="AutoShape 25">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A13B3C8-FC60-4D9C-74C0-5F63B8D21AAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6604000" y="6959600"/>
+          <a:ext cx="762000" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2074" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E0631EB-41FC-4976-4EBD-B64D04A2F2C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="7467600"/>
+          <a:ext cx="292100" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2075" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61AD6C39-B942-7234-7ADC-EEEEEF52AC44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="7975600"/>
+          <a:ext cx="292100" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2076" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE03B4E-01E6-328B-D312-883514B62642}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="8229600"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2077" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9BF1295-C771-CD7D-4E16-ABBB8F0D789E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="9436100"/>
+          <a:ext cx="292100" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2078" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{274CD911-E386-C070-34CB-7CB9DE713F3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="9690100"/>
+          <a:ext cx="292100" cy="177800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2079" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848E6F8B-E7EB-90D2-50CD-7C75ACF836F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="9944100"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2080" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41A2A059-BB6E-328F-C1B4-72937D59B1C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="10198100"/>
+          <a:ext cx="292100" cy="165100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Resim 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A8F1AEA-88AC-5C0B-6195-52C1A14EFB36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="10452100"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2082" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FCB51F0-4DF7-CF0F-7D4D-5733744FB854}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4127500" y="10706100"/>
+          <a:ext cx="292100" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1097,17 +3526,17 @@
       <c r="K1" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>176</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>178</v>
@@ -1120,11 +3549,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>652</v>
+        <v>736</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.50308641975308643</v>
+        <v>0.5679012345679012</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
@@ -1161,6 +3590,9 @@
       <c r="K2" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L2" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -1193,6 +3625,12 @@
       <c r="J3" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1225,6 +3663,12 @@
       <c r="J4" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -1257,6 +3701,12 @@
       <c r="J5" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K5" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1289,6 +3739,12 @@
       <c r="J6" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -1321,6 +3777,12 @@
       <c r="J7" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K7" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1353,6 +3815,12 @@
       <c r="J8" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K8" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -1385,6 +3853,9 @@
       <c r="J9" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L9" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -1417,6 +3888,9 @@
       <c r="J10" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L10" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1449,6 +3923,9 @@
       <c r="J11" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L11" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1481,6 +3958,9 @@
       <c r="J12" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L12" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -1513,6 +3993,9 @@
       <c r="J13" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L13" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1545,6 +4028,9 @@
       <c r="J14" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L14" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1577,6 +4063,9 @@
       <c r="J15" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="L15" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1609,8 +4098,11 @@
       <c r="J16" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L16" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1641,8 +4133,11 @@
       <c r="J17" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L17" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1673,8 +4168,11 @@
       <c r="J18" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L18" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1705,8 +4203,11 @@
       <c r="J19" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L19" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -1737,8 +4238,11 @@
       <c r="J20" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L20" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -1769,8 +4273,11 @@
       <c r="J21" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L21" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -1801,8 +4308,11 @@
       <c r="J22" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L22" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -1833,8 +4343,11 @@
       <c r="J23" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L23" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -1865,8 +4378,11 @@
       <c r="J24" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L24" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -1897,8 +4413,11 @@
       <c r="J25" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L25" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1929,8 +4448,11 @@
       <c r="J26" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L26" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -1961,8 +4483,11 @@
       <c r="J27" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L27" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1993,8 +4518,11 @@
       <c r="J28" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L28" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -2025,8 +4553,11 @@
       <c r="J29" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L29" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -2057,8 +4588,11 @@
       <c r="J30" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L30" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -2089,8 +4623,11 @@
       <c r="J31" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L31" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -2121,8 +4658,11 @@
       <c r="J32" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L32" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -2153,8 +4693,11 @@
       <c r="J33" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L33" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -2185,8 +4728,11 @@
       <c r="J34" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L34" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -2217,11 +4763,11 @@
       <c r="J35" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="K35" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L35" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -2252,11 +4798,11 @@
       <c r="J36" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="K36" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L36" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -2287,11 +4833,11 @@
       <c r="J37" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="K37" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L37" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2322,8 +4868,11 @@
       <c r="J38" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L38" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -2354,8 +4903,11 @@
       <c r="J39" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L39" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -2386,8 +4938,11 @@
       <c r="J40" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L40" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -2418,8 +4973,11 @@
       <c r="J41" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="26" x14ac:dyDescent="0.2">
+      <c r="L41" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -2450,8 +5008,11 @@
       <c r="J42" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L42" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -2482,8 +5043,11 @@
       <c r="J43" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L43" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -2514,8 +5078,11 @@
       <c r="J44" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L44" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -2546,8 +5113,11 @@
       <c r="J45" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L45" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -2578,8 +5148,11 @@
       <c r="J46" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" ht="26" x14ac:dyDescent="0.2">
+      <c r="L46" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="26" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -2610,8 +5183,11 @@
       <c r="J47" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.2">
+      <c r="L47" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
@@ -2642,8 +5218,11 @@
       <c r="J48" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L48" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -2674,8 +5253,11 @@
       <c r="J49" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L49" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -2706,8 +5288,11 @@
       <c r="J50" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L50" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -2738,8 +5323,11 @@
       <c r="J51" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L51" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -2770,8 +5358,11 @@
       <c r="J52" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L52" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -2802,8 +5393,11 @@
       <c r="J53" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L53" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -2834,8 +5428,11 @@
       <c r="J54" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="26" x14ac:dyDescent="0.2">
+      <c r="L54" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="26" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -2866,8 +5463,11 @@
       <c r="J55" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L55" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2898,8 +5498,11 @@
       <c r="J56" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L56" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -2930,8 +5533,11 @@
       <c r="J57" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L57" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -2962,8 +5568,11 @@
       <c r="J58" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L58" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -2994,8 +5603,11 @@
       <c r="J59" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L59" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -3026,8 +5638,11 @@
       <c r="J60" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L60" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -3058,8 +5673,11 @@
       <c r="J61" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L61" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -3090,8 +5708,11 @@
       <c r="J62" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L62" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -3122,8 +5743,11 @@
       <c r="J63" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L63" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
@@ -3154,8 +5778,11 @@
       <c r="J64" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L64" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>128</v>
       </c>
@@ -3186,8 +5813,11 @@
       <c r="J65" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L65" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -3218,8 +5848,11 @@
       <c r="J66" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L66" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>132</v>
       </c>
@@ -3250,8 +5883,11 @@
       <c r="J67" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L67" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
@@ -3282,8 +5918,11 @@
       <c r="J68" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L68" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>136</v>
       </c>
@@ -3314,8 +5953,11 @@
       <c r="J69" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L69" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
@@ -3346,8 +5988,11 @@
       <c r="J70" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L70" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>140</v>
       </c>
@@ -3378,8 +6023,11 @@
       <c r="J71" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L71" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -3410,8 +6058,11 @@
       <c r="J72" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L72" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>144</v>
       </c>
@@ -3442,8 +6093,11 @@
       <c r="J73" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L73" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
@@ -3474,8 +6128,11 @@
       <c r="J74" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L74" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>148</v>
       </c>
@@ -3506,8 +6163,11 @@
       <c r="J75" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L75" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -3538,8 +6198,11 @@
       <c r="J76" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L76" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>152</v>
       </c>
@@ -3570,8 +6233,11 @@
       <c r="J77" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L77" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
@@ -3602,8 +6268,11 @@
       <c r="J78" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L78" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>156</v>
       </c>
@@ -3634,8 +6303,11 @@
       <c r="J79" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L79" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
@@ -3666,8 +6338,11 @@
       <c r="J80" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L80" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>160</v>
       </c>
@@ -3698,8 +6373,11 @@
       <c r="J81" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+      <c r="L81" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
@@ -3728,6 +6406,9 @@
         <v>180</v>
       </c>
       <c r="J82" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="L82" s="8" t="s">
         <v>180</v>
       </c>
     </row>
@@ -3735,4 +6416,488 @@
   <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8BA684-06A3-E24F-8196-0F5126C64EB4}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:D46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C2" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D19" s="13">
+        <v>42131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C22" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C23" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="13">
+        <v>41313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C24" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C25" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D25" s="13">
+        <v>19606</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C26" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C27" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="13">
+        <v>36245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C28" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D28" s="13">
+        <v>40429</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C29" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C30" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" s="13">
+        <v>40932</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C31" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C32" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C33" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C34" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" ht="23" x14ac:dyDescent="0.25">
+      <c r="C36" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C37" s="16"/>
+    </row>
+    <row r="38" spans="3:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="C38" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C39" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C40" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C41" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C42" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C43" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C44" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C45" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C46" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:D34" xr:uid="{AA8BA684-06A3-E24F-8196-0F5126C64EB4}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="2">
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C8:C9"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" tooltip="Pazarkule Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Pazarkule_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{164C58B7-7939-4F4A-8DB2-5811274E9485}"/>
+    <hyperlink ref="C4" r:id="rId2" tooltip="İpsala Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C4%B0psala_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{89DA1D1D-7E12-2541-B4CF-1330319B6958}"/>
+    <hyperlink ref="C5" r:id="rId3" tooltip="Kapıkule Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Kap%C4%B1kule_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{AE6C50B4-B211-1E4C-B7FC-3A98F9473513}"/>
+    <hyperlink ref="C6" r:id="rId4" tooltip="Hamzabeyli Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Hamzabeyli_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{E7F76104-1D82-124B-BDB3-6B7ABAA1C9BA}"/>
+    <hyperlink ref="C7" r:id="rId5" tooltip="Dereköy Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Derek%C3%B6y_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{5CBA874C-C55C-3C48-89F7-D43C0A4F9B58}"/>
+    <hyperlink ref="C8" r:id="rId6" tooltip="Türkgözü Sınır Kapısı" display="https://tr.wikipedia.org/wiki/T%C3%BCrkg%C3%B6z%C3%BC_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{5F2534BD-E965-5147-A4EA-415354597258}"/>
+    <hyperlink ref="D8" r:id="rId7" tooltip="Türkgözü, Posof" display="https://tr.wikipedia.org/wiki/T%C3%BCrkg%C3%B6z%C3%BC,_Posof" xr:uid="{7683EEB8-3B4D-064C-B6F9-D5F780A1975B}"/>
+    <hyperlink ref="C10" r:id="rId8" tooltip="Aktaş Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Akta%C5%9F_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{9483D2B3-394B-B545-9E18-7CD2EE8DE964}"/>
+    <hyperlink ref="D10" r:id="rId9" tooltip="Aktaş Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Akta%C5%9F_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{B12C457B-E708-3740-AB43-0EBC2444007D}"/>
+    <hyperlink ref="C12" r:id="rId10" tooltip="Sarp Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Sarp_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{368F106B-F189-4945-8D10-EE1E468D4E7C}"/>
+    <hyperlink ref="C13" r:id="rId11" tooltip="Dilucu Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Dilucu_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{8C30B7C0-C9F5-8341-B112-4D2FF72B996A}"/>
+    <hyperlink ref="C14" r:id="rId12" tooltip="Gürbulak Sınır Kapısı" display="https://tr.wikipedia.org/wiki/G%C3%BCrbulak_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{F33E624F-37AB-994C-9C2D-D0CF7BEA97C9}"/>
+    <hyperlink ref="C15" r:id="rId13" tooltip="Kapıköy Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Kap%C4%B1k%C3%B6y_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{610B55DF-2D44-F248-9A4E-D7804CA985D4}"/>
+    <hyperlink ref="C16" r:id="rId14" tooltip="Esendere Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Esendere_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{0097F640-7093-1043-96CA-176FF0911589}"/>
+    <hyperlink ref="C17" r:id="rId15" tooltip="Karkamış Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=Karkam%C4%B1%C5%9F_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{7BD9F021-BCF8-FC4B-955B-EDA6F5C07B0A}"/>
+    <hyperlink ref="D17" r:id="rId16" tooltip="Gaziantep" display="https://tr.wikipedia.org/wiki/Gaziantep" xr:uid="{25EBA44B-5F97-E044-B7D7-87D3F130CF6E}"/>
+    <hyperlink ref="C18" r:id="rId17" tooltip="Derecik Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Derecik_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{80DF739C-9035-FF44-AC21-2EC769890DA5}"/>
+    <hyperlink ref="D18" r:id="rId18" tooltip="Hakkâri (il)" display="https://tr.wikipedia.org/wiki/Hakk%C3%A2ri_(il)" xr:uid="{25E13E74-E827-614F-9C23-AEDCC92A4711}"/>
+    <hyperlink ref="C19" r:id="rId19" tooltip="Üzümlü Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C3%9Cz%C3%BCml%C3%BC_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{9BDFE3F3-B7D0-3443-85A3-4C7DE0B4B5D2}"/>
+    <hyperlink ref="C20" r:id="rId20" tooltip="Yayladağı Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Yaylada%C4%9F%C4%B1_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{6FF2B7FC-72D0-3647-8EEA-73B0F4F28FD8}"/>
+    <hyperlink ref="C21" r:id="rId21" tooltip="Cilvegözü Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Cilveg%C3%B6z%C3%BC_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{02D8FCE3-8D89-794C-B62B-BF612BAAB11E}"/>
+    <hyperlink ref="C22" r:id="rId22" tooltip="Öncüpınar Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C3%96nc%C3%BCp%C4%B1nar_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{A8E9F606-7353-8041-8ABF-52498F8376A2}"/>
+    <hyperlink ref="D22" r:id="rId23" tooltip="Kilis (il)" display="https://tr.wikipedia.org/wiki/Kilis_(il)" xr:uid="{6C3D3F57-17FC-B648-B98C-DF43C08B76A6}"/>
+    <hyperlink ref="C23" r:id="rId24" tooltip="Çobanbey Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C3%87obanbey_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{0CDB7DAE-9858-8746-B5C9-53A046247DAC}"/>
+    <hyperlink ref="C24" r:id="rId25" tooltip="Nusaybin Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=Nusaybin_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{96B15A3B-DA07-494B-9F24-E0CD71863BB7}"/>
+    <hyperlink ref="D24" r:id="rId26" tooltip="Mardin" display="https://tr.wikipedia.org/wiki/Mardin" xr:uid="{2EADE234-F0B6-6E4D-9E50-669BFE440A09}"/>
+    <hyperlink ref="C25" r:id="rId27" tooltip="Şenyurt Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=%C5%9Eenyurt_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{3D5C6041-388E-884D-94BC-9264529A1AA1}"/>
+    <hyperlink ref="C26" r:id="rId28" tooltip="Akçakale Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Ak%C3%A7akale_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{32188BE4-8149-724A-AA2C-5CBF4A6A7BFF}"/>
+    <hyperlink ref="D26" r:id="rId29" tooltip="Şanlıurfa" display="https://tr.wikipedia.org/wiki/%C5%9Eanl%C4%B1urfa" xr:uid="{7E921895-7E40-664C-B223-CD9025D3BE50}"/>
+    <hyperlink ref="C27" r:id="rId30" tooltip="Ceylanpınar Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=Ceylanp%C4%B1nar_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{5D58917C-0134-4F4C-A6A9-AEB7FD6F0CEE}"/>
+    <hyperlink ref="C28" r:id="rId31" tooltip="Mürşitpınar Sınır Kapısı" display="https://tr.wikipedia.org/wiki/M%C3%BCr%C5%9Fitp%C4%B1nar_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{E31D39AB-40AB-1D47-AB66-2D00173CF042}"/>
+    <hyperlink ref="C29" r:id="rId32" tooltip="Habur Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Habur_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{2F005F90-57C5-C548-BF7C-67CD0AC06BE3}"/>
+    <hyperlink ref="C30" r:id="rId33" tooltip="Gülyazı Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=G%C3%BClyaz%C4%B1_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{C2B44892-0DA7-4146-B148-D409CF87A866}"/>
+    <hyperlink ref="C31" r:id="rId34" tooltip="Akyaka Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Akyaka_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{CA0C53F0-F9DE-FC46-A05C-E0264145471C}"/>
+    <hyperlink ref="D31" r:id="rId35" tooltip="Kars (il)" display="https://tr.wikipedia.org/wiki/Kars_(il)" xr:uid="{3C8C05B9-9232-6540-AD1D-EE085F2060FD}"/>
+    <hyperlink ref="C32" r:id="rId36" tooltip="Alican Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Alican_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{A6CBD796-E3AE-A94E-8562-17890F9C27BC}"/>
+    <hyperlink ref="C33" r:id="rId37" tooltip="Borualan Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Borualan_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{966B6F46-1479-5441-AF65-40F28852A9F2}"/>
+    <hyperlink ref="D33" r:id="rId38" tooltip="Iğdır (il)" display="https://tr.wikipedia.org/wiki/I%C4%9Fd%C4%B1r_(il)" xr:uid="{946B11C4-457D-6845-B92D-47098D5C6E3E}"/>
+    <hyperlink ref="C34" r:id="rId39" tooltip="Zeytindalı Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=Zeytindal%C4%B1_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{021BAFFE-889B-6948-8DF8-46DB04E242F3}"/>
+    <hyperlink ref="D34" r:id="rId40" tooltip="Hatay" display="https://tr.wikipedia.org/wiki/Hatay" xr:uid="{685BC75C-F796-9C4E-9C6D-7259B42B4CA2}"/>
+    <hyperlink ref="C39" r:id="rId41" tooltip="Akyaka Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Akyaka_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{B093C4D6-EBDB-8842-A328-4B9F4C9E6FE3}"/>
+    <hyperlink ref="D39" r:id="rId42" tooltip="Kars (il)" display="https://tr.wikipedia.org/wiki/Kars_(il)" xr:uid="{8D7C5591-4E40-E54D-AC77-59249FF43569}"/>
+    <hyperlink ref="C40" r:id="rId43" tooltip="Kapıkule Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Kap%C4%B1kule_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{859F8404-1A72-364D-8429-D00C6D8E0D08}"/>
+    <hyperlink ref="D40" r:id="rId44" tooltip="Edirne (il)" display="https://tr.wikipedia.org/wiki/Edirne_(il)" xr:uid="{4E4073D5-4E57-1442-AEC5-75D891F3778B}"/>
+    <hyperlink ref="C41" r:id="rId45" tooltip="Aktaş Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Akta%C5%9F_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{1947E0D2-2AEF-DC49-B1D0-45F002BDC528}"/>
+    <hyperlink ref="D41" r:id="rId46" tooltip="Ardahan (il)" display="https://tr.wikipedia.org/wiki/Ardahan_(il)" xr:uid="{5CA19175-095B-4646-8FE8-F97ABB777BC2}"/>
+    <hyperlink ref="C42" r:id="rId47" tooltip="Kapıköy Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Kap%C4%B1k%C3%B6y_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{4A439E31-4EAE-DE47-ABC1-E7E76A83811A}"/>
+    <hyperlink ref="D42" r:id="rId48" tooltip="Van" display="https://tr.wikipedia.org/wiki/Van" xr:uid="{6CA5CF00-DA33-6C46-9229-CD37B7D81258}"/>
+    <hyperlink ref="C43" r:id="rId49" tooltip="Uzunköprü Sınır Kapısı" display="https://tr.wikipedia.org/wiki/Uzunk%C3%B6pr%C3%BC_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{995B4EBF-44AE-4C4D-925D-608F16C1F138}"/>
+    <hyperlink ref="D43" r:id="rId50" tooltip="Edirne (il)" display="https://tr.wikipedia.org/wiki/Edirne_(il)" xr:uid="{892626EF-D420-BE40-9A5A-3B0AF68C168C}"/>
+    <hyperlink ref="C44" r:id="rId51" tooltip="İslahiye Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C4%B0slahiye_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{A4F3F427-874C-9948-8C88-D2A8A63ABBDB}"/>
+    <hyperlink ref="D44" r:id="rId52" tooltip="Gaziantep" display="https://tr.wikipedia.org/wiki/Gaziantep" xr:uid="{E029DB01-C0C5-8C49-A19C-5FCF0DF1FCD0}"/>
+    <hyperlink ref="C45" r:id="rId53" tooltip="Çobanbey Sınır Kapısı" display="https://tr.wikipedia.org/wiki/%C3%87obanbey_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1" xr:uid="{7BA4EF34-7DFB-0B4D-9E0C-EC19113C3F35}"/>
+    <hyperlink ref="D45" r:id="rId54" tooltip="Kilis (il)" display="https://tr.wikipedia.org/wiki/Kilis_(il)" xr:uid="{4C18F81D-2E8A-9645-8DD5-1328D2F18CDA}"/>
+    <hyperlink ref="C46" r:id="rId55" tooltip="Nusaybin Sınır Kapısı (sayfa mevcut değil)" display="https://tr.wikipedia.org/w/index.php?title=Nusaybin_S%C4%B1n%C4%B1r_Kap%C4%B1s%C4%B1&amp;action=edit&amp;redlink=1" xr:uid="{C8DC1473-6683-384F-A701-19DFFC258D90}"/>
+    <hyperlink ref="D46" r:id="rId56" tooltip="Mardin" display="https://tr.wikipedia.org/wiki/Mardin" xr:uid="{3B21F13B-DCF5-204C-9C2B-977029AFCB29}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId57"/>
+</worksheet>
 </file>
--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6EDE9F-DE7C-FB4D-9966-E2CE00FE0656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EAF50D-99FF-AB4C-AC7C-310C02BEB2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3483,10 +3483,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="19" width="10.83203125" style="8"/>
+    <col min="1" max="2" width="10.83203125" style="8"/>
+    <col min="3" max="10" width="0" style="8" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="8"/>
+    <col min="12" max="12" width="0" style="8" hidden="1" customWidth="1"/>
+    <col min="13" max="19" width="10.83203125" style="8"/>
     <col min="20" max="20" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="16384" width="10.83203125" style="8"/>
@@ -3529,14 +3534,14 @@
       <c r="L1" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>176</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>178</v>
@@ -3549,14 +3554,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>736</v>
+        <v>777</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.5679012345679012</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+        <v>0.59953703703703709</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3593,8 +3598,11 @@
       <c r="L2" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="M2" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3631,8 +3639,11 @@
       <c r="L3" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="26" x14ac:dyDescent="0.2">
+      <c r="M3" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3669,8 +3680,11 @@
       <c r="L4" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="M4" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3708,7 +3722,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3746,7 +3760,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3784,7 +3798,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -3822,7 +3836,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -3853,11 +3867,14 @@
       <c r="J9" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K9" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L9" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3888,11 +3905,14 @@
       <c r="J10" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K10" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L10" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -3923,11 +3943,14 @@
       <c r="J11" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K11" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L11" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -3958,11 +3981,14 @@
       <c r="J12" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K12" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L12" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -3993,11 +4019,14 @@
       <c r="J13" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K13" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="L13" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -4028,11 +4057,14 @@
       <c r="J14" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K14" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L14" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -4063,11 +4095,14 @@
       <c r="J15" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K15" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L15" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -4098,11 +4133,14 @@
       <c r="J16" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K16" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="L16" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -4133,11 +4171,14 @@
       <c r="J17" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K17" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L17" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -4168,11 +4209,14 @@
       <c r="J18" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K18" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L18" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -4203,11 +4247,14 @@
       <c r="J19" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K19" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L19" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -4238,11 +4285,14 @@
       <c r="J20" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K20" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L20" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -4273,11 +4323,14 @@
       <c r="J21" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K21" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L21" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -4308,11 +4361,14 @@
       <c r="J22" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K22" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L22" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -4343,11 +4399,14 @@
       <c r="J23" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K23" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L23" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -4378,11 +4437,14 @@
       <c r="J24" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K24" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L24" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -4413,11 +4475,14 @@
       <c r="J25" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K25" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L25" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -4448,11 +4513,14 @@
       <c r="J26" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K26" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L26" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -4483,11 +4551,14 @@
       <c r="J27" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K27" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L27" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -4518,11 +4589,14 @@
       <c r="J28" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K28" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L28" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -4553,11 +4627,14 @@
       <c r="J29" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K29" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L29" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -4588,11 +4665,14 @@
       <c r="J30" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K30" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L30" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -4623,11 +4703,14 @@
       <c r="J31" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K31" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L31" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -4658,11 +4741,14 @@
       <c r="J32" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K32" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L32" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -4693,11 +4779,14 @@
       <c r="J33" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K33" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="L33" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4728,11 +4817,14 @@
       <c r="J34" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K34" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L34" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -4763,11 +4855,14 @@
       <c r="J35" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K35" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L35" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -4798,11 +4893,14 @@
       <c r="J36" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K36" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L36" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -4833,11 +4931,14 @@
       <c r="J37" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K37" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L37" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -4868,11 +4969,14 @@
       <c r="J38" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K38" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L38" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -4903,11 +5007,14 @@
       <c r="J39" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K39" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L39" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -4938,11 +5045,14 @@
       <c r="J40" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K40" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L40" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -4973,11 +5083,14 @@
       <c r="J41" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K41" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L41" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="26" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -5006,6 +5119,9 @@
         <v>180</v>
       </c>
       <c r="J42" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K42" s="8" t="s">
         <v>180</v>
       </c>
       <c r="L42" s="8" t="s">
@@ -5043,6 +5159,9 @@
       <c r="J43" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K43" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L43" s="8" t="s">
         <v>180</v>
       </c>
@@ -5078,11 +5197,14 @@
       <c r="J44" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K44" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L44" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -5111,6 +5233,9 @@
         <v>180</v>
       </c>
       <c r="J45" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="8" t="s">
         <v>180</v>
       </c>
       <c r="L45" s="8" t="s">
@@ -5148,6 +5273,9 @@
       <c r="J46" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K46" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L46" s="8" t="s">
         <v>180</v>
       </c>
@@ -6413,7 +6541,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+    <filterColumn colId="10">
+      <filters blank="1"/>
+    </filterColumn>
+    <filterColumn colId="12">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EAF50D-99FF-AB4C-AC7C-310C02BEB2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23690E99-0745-FE43-B006-D139BE6D309C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3483,15 +3483,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="8"/>
-    <col min="3" max="10" width="0" style="8" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="8"/>
-    <col min="12" max="12" width="0" style="8" hidden="1" customWidth="1"/>
-    <col min="13" max="19" width="10.83203125" style="8"/>
+    <col min="1" max="1" width="10.83203125" style="8"/>
+    <col min="2" max="2" width="19.5" style="8" customWidth="1"/>
+    <col min="3" max="12" width="0" style="8" hidden="1" customWidth="1"/>
+    <col min="13" max="16" width="10.83203125" style="8"/>
+    <col min="17" max="17" width="0" style="8" hidden="1" customWidth="1"/>
+    <col min="18" max="19" width="10.83203125" style="8"/>
     <col min="20" max="20" width="3.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="16384" width="10.83203125" style="8"/>
@@ -3554,14 +3554,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>777</v>
+        <v>891</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.59953703703703709</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3721,8 +3721,11 @@
       <c r="L5" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3759,8 +3762,11 @@
       <c r="L6" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M6" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3797,8 +3803,11 @@
       <c r="L7" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -3835,8 +3844,11 @@
       <c r="L8" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -3873,8 +3885,11 @@
       <c r="L9" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M9" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3911,8 +3926,11 @@
       <c r="L10" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M10" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -3949,8 +3967,11 @@
       <c r="L11" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -3987,8 +4008,11 @@
       <c r="L12" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M12" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -4020,13 +4044,16 @@
         <v>180</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -4063,8 +4090,11 @@
       <c r="L14" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M14" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -4101,8 +4131,11 @@
       <c r="L15" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M15" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -4134,13 +4167,16 @@
         <v>180</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -4177,8 +4213,11 @@
       <c r="L17" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -4215,8 +4254,11 @@
       <c r="L18" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -4253,8 +4295,11 @@
       <c r="L19" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -4291,8 +4336,11 @@
       <c r="L20" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -4329,8 +4377,11 @@
       <c r="L21" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -4367,8 +4418,11 @@
       <c r="L22" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -4405,8 +4459,11 @@
       <c r="L23" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M23" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -4443,8 +4500,11 @@
       <c r="L24" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -4481,8 +4541,11 @@
       <c r="L25" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M25" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -4519,8 +4582,11 @@
       <c r="L26" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M26" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -4557,8 +4623,11 @@
       <c r="L27" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M27" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -4595,8 +4664,11 @@
       <c r="L28" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M28" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -4633,8 +4705,11 @@
       <c r="L29" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M29" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -4671,8 +4746,11 @@
       <c r="L30" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M30" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -4709,8 +4787,11 @@
       <c r="L31" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M31" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -4747,8 +4828,11 @@
       <c r="L32" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M32" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -4780,13 +4864,16 @@
         <v>180</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M33" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4823,8 +4910,11 @@
       <c r="L34" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M34" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -4861,8 +4951,11 @@
       <c r="L35" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M35" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -4899,8 +4992,11 @@
       <c r="L36" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M36" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -4937,8 +5033,11 @@
       <c r="L37" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M37" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -4975,8 +5074,11 @@
       <c r="L38" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M38" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -5013,8 +5115,11 @@
       <c r="L39" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M39" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -5051,8 +5156,11 @@
       <c r="L40" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M40" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -5089,8 +5197,11 @@
       <c r="L41" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="26" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M41" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -5127,8 +5238,11 @@
       <c r="L42" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M42" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -5165,8 +5279,11 @@
       <c r="L43" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M43" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -5203,8 +5320,11 @@
       <c r="L44" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" ht="14" hidden="1" x14ac:dyDescent="0.2">
+      <c r="M44" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -5241,8 +5361,11 @@
       <c r="L45" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M45" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -5279,8 +5402,11 @@
       <c r="L46" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="26" x14ac:dyDescent="0.2">
+      <c r="M46" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -5311,11 +5437,17 @@
       <c r="J47" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K47" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L47" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M47" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
@@ -5346,11 +5478,17 @@
       <c r="J48" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K48" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L48" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M48" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -5381,11 +5519,17 @@
       <c r="J49" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K49" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L49" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M49" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -5416,11 +5560,17 @@
       <c r="J50" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K50" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L50" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M50" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -5451,11 +5601,17 @@
       <c r="J51" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K51" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L51" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M51" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -5486,11 +5642,17 @@
       <c r="J52" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K52" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L52" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M52" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -5521,11 +5683,17 @@
       <c r="J53" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K53" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L53" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M53" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -5556,11 +5724,17 @@
       <c r="J54" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K54" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L54" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" ht="26" x14ac:dyDescent="0.2">
+      <c r="M54" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -5591,11 +5765,17 @@
       <c r="J55" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K55" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L55" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M55" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -5626,11 +5806,17 @@
       <c r="J56" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K56" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L56" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M56" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -5661,11 +5847,17 @@
       <c r="J57" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K57" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L57" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M57" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -5696,11 +5888,17 @@
       <c r="J58" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K58" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L58" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M58" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -5731,11 +5929,17 @@
       <c r="J59" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K59" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L59" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M59" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -5766,11 +5970,17 @@
       <c r="J60" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K60" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L60" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M60" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -5801,11 +6011,17 @@
       <c r="J61" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K61" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L61" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M61" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -5836,11 +6052,17 @@
       <c r="J62" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K62" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L62" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M62" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -5871,11 +6093,17 @@
       <c r="J63" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K63" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L63" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M63" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
@@ -5906,11 +6134,17 @@
       <c r="J64" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K64" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L64" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M64" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>128</v>
       </c>
@@ -5941,11 +6175,17 @@
       <c r="J65" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K65" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L65" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M65" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
@@ -5976,11 +6216,17 @@
       <c r="J66" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K66" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L66" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M66" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>132</v>
       </c>
@@ -6011,11 +6257,17 @@
       <c r="J67" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K67" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L67" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M67" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
@@ -6046,11 +6298,17 @@
       <c r="J68" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K68" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L68" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M68" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>136</v>
       </c>
@@ -6081,11 +6339,17 @@
       <c r="J69" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K69" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L69" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M69" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
@@ -6116,11 +6380,17 @@
       <c r="J70" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K70" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L70" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M70" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>140</v>
       </c>
@@ -6151,11 +6421,17 @@
       <c r="J71" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K71" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L71" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M71" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
@@ -6186,11 +6462,17 @@
       <c r="J72" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K72" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L72" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M72" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>144</v>
       </c>
@@ -6221,11 +6503,17 @@
       <c r="J73" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K73" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L73" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M73" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
@@ -6256,11 +6544,17 @@
       <c r="J74" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K74" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L74" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M74" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>148</v>
       </c>
@@ -6291,11 +6585,17 @@
       <c r="J75" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K75" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L75" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M75" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
@@ -6326,11 +6626,17 @@
       <c r="J76" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K76" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L76" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M76" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>152</v>
       </c>
@@ -6361,11 +6667,17 @@
       <c r="J77" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K77" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L77" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M77" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
@@ -6396,11 +6708,17 @@
       <c r="J78" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K78" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L78" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M78" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>156</v>
       </c>
@@ -6431,11 +6749,17 @@
       <c r="J79" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K79" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L79" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M79" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
@@ -6466,11 +6790,17 @@
       <c r="J80" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K80" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L80" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M80" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>160</v>
       </c>
@@ -6501,11 +6831,17 @@
       <c r="J81" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K81" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L81" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+      <c r="M81" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
@@ -6536,19 +6872,18 @@
       <c r="J82" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="K82" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="L82" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="M82" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
-    <filterColumn colId="10">
-      <filters blank="1"/>
-    </filterColumn>
-    <filterColumn colId="12">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23690E99-0745-FE43-B006-D139BE6D309C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE84E66-9584-2341-8BF4-70828D2053CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3483,6 +3483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3554,14 +3555,14 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+        <v>0.70370370370370372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3601,8 +3602,14 @@
       <c r="M2" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="N2" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3642,8 +3649,11 @@
       <c r="M3" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O3" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3683,8 +3693,11 @@
       <c r="M4" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O4" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3724,8 +3737,11 @@
       <c r="M5" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O5" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3765,8 +3781,11 @@
       <c r="M6" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O6" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3806,8 +3825,11 @@
       <c r="M7" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O7" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -3847,8 +3869,11 @@
       <c r="M8" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O8" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -3888,8 +3913,11 @@
       <c r="M9" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O9" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3929,8 +3957,11 @@
       <c r="M10" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O10" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -3970,8 +4001,11 @@
       <c r="M11" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O11" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -4011,8 +4045,11 @@
       <c r="M12" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O12" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -4052,8 +4089,11 @@
       <c r="M13" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O13" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -4093,8 +4133,11 @@
       <c r="M14" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O14" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -4134,8 +4177,11 @@
       <c r="M15" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="O15" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -4175,8 +4221,11 @@
       <c r="M16" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O16" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -4216,8 +4265,11 @@
       <c r="M17" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O17" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -4257,8 +4309,11 @@
       <c r="M18" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O18" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -4298,8 +4353,11 @@
       <c r="M19" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O19" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
@@ -4339,8 +4397,11 @@
       <c r="M20" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O20" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -4380,8 +4441,11 @@
       <c r="M21" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O21" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -4422,7 +4486,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -4463,7 +4527,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -4504,7 +4568,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -4545,7 +4609,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -4586,7 +4650,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -4627,7 +4691,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -4668,7 +4732,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -4709,7 +4773,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -4750,7 +4814,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -4791,7 +4855,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -6883,7 +6947,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}"/>
+  <autoFilter ref="A1:R82" xr:uid="{23195AC8-2F0C-244B-8F3F-FBCB0ABA6978}">
+    <filterColumn colId="14">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE84E66-9584-2341-8BF4-70828D2053CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577E5400-CBA7-954B-99E3-434CBA0FB7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -1425,9 +1425,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Köprü" xfId="3" builtinId="8"/>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.70370370370370372</v>
+        <v>0.70756172839506171</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -4445,7 +4445,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -4485,8 +4485,11 @@
       <c r="M22" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+      <c r="O22" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -4526,8 +4529,11 @@
       <c r="M23" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+      <c r="O23" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -4565,6 +4571,9 @@
         <v>180</v>
       </c>
       <c r="M24" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="O24" s="8" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4608,6 +4617,9 @@
       <c r="M25" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O25" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="26" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -4647,6 +4659,9 @@
         <v>180</v>
       </c>
       <c r="M26" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>180</v>
       </c>
     </row>
@@ -7034,7 +7049,7 @@
       <c r="B8" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="16" t="s">
         <v>194</v>
       </c>
       <c r="D8" s="12" t="s">
@@ -7045,7 +7060,7 @@
       <c r="B9" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="11" t="s">
         <v>196</v>
       </c>
@@ -7054,7 +7069,7 @@
       <c r="B10" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="16" t="s">
         <v>197</v>
       </c>
       <c r="D10" s="12" t="s">
@@ -7065,7 +7080,7 @@
       <c r="B11" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="11" t="s">
         <v>199</v>
       </c>
@@ -7288,12 +7303,12 @@
       </c>
     </row>
     <row r="36" spans="3:4" ht="23" x14ac:dyDescent="0.25">
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C37" s="16"/>
+      <c r="C37" s="15"/>
     </row>
     <row r="38" spans="3:4" ht="20" x14ac:dyDescent="0.2">
       <c r="C38" s="10" t="s">

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577E5400-CBA7-954B-99E3-434CBA0FB7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C3023-F176-7144-AF5A-D6D1CAA67E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.70756172839506171</v>
+        <v>0.71682098765432101</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -4705,6 +4705,9 @@
       <c r="M27" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O27" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="28" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -4746,6 +4749,9 @@
       <c r="M28" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O28" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="29" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
@@ -4787,6 +4793,9 @@
       <c r="M29" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O29" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="30" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -4828,6 +4837,9 @@
       <c r="M30" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O30" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="31" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
@@ -4869,6 +4881,9 @@
       <c r="M31" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O31" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="32" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -4910,8 +4925,11 @@
       <c r="M32" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O32" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -4951,8 +4969,11 @@
       <c r="M33" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O33" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4992,8 +5013,11 @@
       <c r="M34" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O34" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -5033,8 +5057,11 @@
       <c r="M35" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O35" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -5074,8 +5101,11 @@
       <c r="M36" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O36" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -5115,8 +5145,11 @@
       <c r="M37" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O37" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -5156,8 +5189,11 @@
       <c r="M38" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O38" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -5198,7 +5234,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -5239,7 +5275,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
@@ -5280,7 +5316,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -5321,7 +5357,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>84</v>
       </c>
@@ -5362,7 +5398,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -5403,7 +5439,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>88</v>
       </c>
@@ -5444,7 +5480,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -5485,7 +5521,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>92</v>
       </c>
@@ -5526,7 +5562,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674C3023-F176-7144-AF5A-D6D1CAA67E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891D4C01-6C29-A14B-8B99-9F8A196B097A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.71682098765432101</v>
+        <v>0.71836419753086422</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -4577,7 +4577,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>60</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>64</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>68</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>72</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>76</v>
       </c>
@@ -5233,8 +5233,11 @@
       <c r="M39" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="14" x14ac:dyDescent="0.2">
+      <c r="O39" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="14" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -5272,6 +5275,9 @@
         <v>180</v>
       </c>
       <c r="M40" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>180</v>
       </c>
     </row>

--- a/poi işleme.xlsx
+++ b/poi işleme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bayramdede/yukegel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891D4C01-6C29-A14B-8B99-9F8A196B097A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200EF8C8-D276-0642-ABA1-340ED24FDE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19460" xr2:uid="{E1D972E4-1409-ED40-89CA-F08F30BA43A7}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="247">
   <si>
     <t>İL PLAKA NO</t>
   </si>
@@ -3555,11 +3555,11 @@
       </c>
       <c r="T1" s="8">
         <f>COUNTA(C2:R82)</f>
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="U1" s="9">
         <f>+T1/81/16</f>
-        <v>0.71836419753086422</v>
+        <v>0.73302469135802473</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="14" hidden="1" x14ac:dyDescent="0.2">
@@ -5321,6 +5321,9 @@
       <c r="M41" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O41" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="42" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
@@ -5362,6 +5365,9 @@
       <c r="M42" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O42" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="43" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -5403,6 +5409,9 @@
       <c r="M43" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O43" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="44" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5444,6 +5453,9 @@
       <c r="M44" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O44" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="45" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -5485,6 +5497,9 @@
       <c r="M45" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O45" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="46" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5526,6 +5541,9 @@
       <c r="M46" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O46" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="47" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
@@ -5567,6 +5585,9 @@
       <c r="M47" s="8" t="s">
         <v>180</v>
       </c>
+      <c r="O47" s="8" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="48" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5608,8 +5629,11 @@
       <c r="M48" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O48" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>96</v>
       </c>
@@ -5649,8 +5673,11 @@
       <c r="M49" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O49" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
@@ -5690,8 +5717,11 @@
       <c r="M50" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O50" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>100</v>
       </c>
@@ -5731,8 +5761,11 @@
       <c r="M51" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O51" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
@@ -5772,8 +5805,11 @@
       <c r="M52" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O52" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>104</v>
       </c>
@@ -5813,8 +5849,11 @@
       <c r="M53" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O53" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -5854,8 +5893,11 @@
       <c r="M54" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O54" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>108</v>
       </c>
@@ -5895,8 +5937,11 @@
       <c r="M55" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O55" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -5936,8 +5981,11 @@
       <c r="M56" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O56" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>112</v>
       </c>
@@ -5977,8 +6025,11 @@
       <c r="M57" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O57" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
@@ -6018,8 +6069,11 @@
       <c r="M58" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O58" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>116</v>
       </c>
@@ -6059,8 +6113,11 @@
       <c r="M59" s="8" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+      <c r="O59" s="8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
@@ -6101,7 +6158,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>120</v>
       </c>
@@ -6142,7 +6199,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
@@ -6183,7 +6240,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>124</v>
       </c>
@@ -6224,7 +6281,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
